--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,6 +315,9 @@
     <t>Extension.url</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">uri
 </t>
   </si>
@@ -332,9 +335,6 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">markdown
@@ -1144,7 +1144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1246,15 +1246,15 @@
         <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1268,7 +1268,7 @@
         <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1334,7 +1334,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1349,7 +1349,7 @@
         <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-rezeptur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
